--- a/data/trans_camb/IP04D$aparatos-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$aparatos-Edad-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 5,1</t>
+          <t>-13,58; 4,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 8,57</t>
+          <t>-15,07; 8,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 10,65</t>
+          <t>-9,91; 9,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 19,19</t>
+          <t>-5,77; 17,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 5,17</t>
+          <t>-9,23; 4,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 10,41</t>
+          <t>-6,6; 9,49</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,05; 9,1</t>
+          <t>-21,13; 8,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,75; 14,92</t>
+          <t>-23,27; 15,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 21,36</t>
+          <t>-16,63; 20,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 38,37</t>
+          <t>-9,96; 36,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,04; 9,33</t>
+          <t>-15,34; 7,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 19,26</t>
+          <t>-11,28; 17,35</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-25,86; -11,31</t>
+          <t>-26,48; -11,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 2,26</t>
+          <t>-14,0; 2,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,14; -5,39</t>
+          <t>-19,57; -5,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 6,89</t>
+          <t>-7,39; 7,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,46; -10,08</t>
+          <t>-20,2; -9,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 2,8</t>
+          <t>-8,79; 2,98</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,31; -18,12</t>
+          <t>-37,95; -17,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,82; 3,47</t>
+          <t>-20,24; 3,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,86; -8,52</t>
+          <t>-28,44; -9,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 11,05</t>
+          <t>-10,84; 12,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,94; -15,71</t>
+          <t>-29,66; -15,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 4,38</t>
+          <t>-12,85; 4,61</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-19,34; -1,14</t>
+          <t>-18,1; -1,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 11,97</t>
+          <t>-6,26; 11,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 0,56</t>
+          <t>-17,33; -0,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 2,97</t>
+          <t>-15,2; 3,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,31; -2,33</t>
+          <t>-15,61; -2,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 3,88</t>
+          <t>-8,68; 4,4</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-28,84; -2,03</t>
+          <t>-27,41; -2,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 20,84</t>
+          <t>-9,15; 19,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-27,05; 1,11</t>
+          <t>-27,0; 0,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,92; 5,67</t>
+          <t>-24,05; 6,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-23,64; -3,78</t>
+          <t>-24,44; -5,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 6,79</t>
+          <t>-13,61; 7,69</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-22,18; -4,78</t>
+          <t>-21,54; -4,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 10,69</t>
+          <t>-11,63; 10,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,27; -2,56</t>
+          <t>-21,17; -4,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 1,56</t>
+          <t>-17,64; 2,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-18,72; -6,53</t>
+          <t>-18,8; -6,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 3,96</t>
+          <t>-11,75; 3,42</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-33,69; -8,37</t>
+          <t>-31,82; -7,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,42; 17,96</t>
+          <t>-17,21; 17,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-30,2; -4,37</t>
+          <t>-31,02; -6,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,11; 2,64</t>
+          <t>-26,11; 3,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,24; -10,67</t>
+          <t>-27,93; -10,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 6,45</t>
+          <t>-17,48; 5,5</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-16,72; -7,9</t>
+          <t>-16,5; -7,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 4,09</t>
+          <t>-6,65; 4,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,06; -4,8</t>
+          <t>-13,46; -5,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 1,46</t>
+          <t>-8,36; 1,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,92; -7,73</t>
+          <t>-13,89; -7,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 0,87</t>
+          <t>-6,69; 0,75</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-25,27; -12,66</t>
+          <t>-24,84; -12,81</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 6,5</t>
+          <t>-10,04; 7,01</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-20,56; -8,01</t>
+          <t>-21,1; -8,56</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 2,47</t>
+          <t>-13,15; 1,95</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-21,54; -12,49</t>
+          <t>-21,77; -12,72</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 1,42</t>
+          <t>-10,34; 1,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$aparatos-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$aparatos-Edad-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 4,91</t>
+          <t>-14,51; 5,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 8,73</t>
+          <t>-14,11; 8,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 9,97</t>
+          <t>-9,65; 10,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 17,8</t>
+          <t>-6,75; 16,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 4,22</t>
+          <t>-8,56; 5,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 9,49</t>
+          <t>-6,97; 9,52</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,13; 8,55</t>
+          <t>-21,95; 8,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,27; 15,32</t>
+          <t>-21,99; 15,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,63; 20,37</t>
+          <t>-16,65; 21,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 36,18</t>
+          <t>-11,53; 32,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 7,66</t>
+          <t>-14,06; 9,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 17,35</t>
+          <t>-11,8; 17,26</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-26,48; -11,3</t>
+          <t>-26,4; -10,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 2,14</t>
+          <t>-14,4; 2,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,57; -5,85</t>
+          <t>-19,62; -6,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 7,97</t>
+          <t>-7,25; 7,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,2; -9,88</t>
+          <t>-20,23; -9,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 2,98</t>
+          <t>-8,42; 2,55</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,95; -17,89</t>
+          <t>-37,48; -17,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,24; 3,3</t>
+          <t>-21,08; 3,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,44; -9,57</t>
+          <t>-28,65; -9,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 12,76</t>
+          <t>-10,84; 12,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,66; -15,45</t>
+          <t>-29,59; -15,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 4,61</t>
+          <t>-12,47; 4,02</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,1; -1,74</t>
+          <t>-18,87; -0,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 11,83</t>
+          <t>-6,23; 11,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,33; -0,01</t>
+          <t>-16,88; 0,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,2; 3,57</t>
+          <t>-15,03; 3,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,61; -2,83</t>
+          <t>-15,04; -2,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 4,4</t>
+          <t>-8,63; 4,22</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-27,41; -2,94</t>
+          <t>-28,0; -1,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 19,9</t>
+          <t>-8,71; 20,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-27,0; 0,55</t>
+          <t>-26,65; 0,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,05; 6,87</t>
+          <t>-24,28; 5,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,44; -5,2</t>
+          <t>-23,46; -4,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 7,69</t>
+          <t>-13,47; 7,14</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-21,54; -4,67</t>
+          <t>-22,49; -5,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 10,37</t>
+          <t>-11,49; 10,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-21,17; -4,11</t>
+          <t>-20,11; -3,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 2,27</t>
+          <t>-17,49; 1,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-18,8; -6,93</t>
+          <t>-18,84; -6,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 3,42</t>
+          <t>-11,11; 3,6</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-31,82; -7,87</t>
+          <t>-32,73; -8,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,21; 17,31</t>
+          <t>-17,16; 18,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-31,02; -6,81</t>
+          <t>-29,94; -4,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,11; 3,58</t>
+          <t>-25,81; 3,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-27,93; -10,97</t>
+          <t>-28,49; -10,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-17,48; 5,5</t>
+          <t>-16,9; 5,78</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-16,5; -7,96</t>
+          <t>-16,94; -8,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 4,3</t>
+          <t>-6,69; 4,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,46; -5,19</t>
+          <t>-13,31; -5,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 1,36</t>
+          <t>-8,57; 1,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,89; -7,73</t>
+          <t>-13,77; -7,92</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 0,75</t>
+          <t>-5,76; 1,24</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-24,84; -12,81</t>
+          <t>-25,55; -12,95</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 7,01</t>
+          <t>-10,29; 6,93</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-21,1; -8,56</t>
+          <t>-20,81; -8,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 1,95</t>
+          <t>-13,79; 2,36</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-21,77; -12,72</t>
+          <t>-21,45; -12,79</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 1,25</t>
+          <t>-9,08; 1,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$aparatos-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$aparatos-Edad-trans_camb.xlsx
@@ -511,19 +511,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no dispone de instalación de calefacción en su vivienda pero sí tiene aparatos de calefacción</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -591,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,53</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,24</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-4,72</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-2,74</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,53</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,81</t>
+          <t>-3,28</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -616,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,57</t>
+          <t>1,96</t>
         </is>
       </c>
     </row>
@@ -629,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 5,07</t>
+          <t>-9,23; 10,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 8,97</t>
+          <t>-4,92; 20,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 10,39</t>
+          <t>-14,43; 5,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 16,64</t>
+          <t>-15,95; 8,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 5,08</t>
+          <t>-8,55; 5,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 9,52</t>
+          <t>-6,46; 10,49</t>
         </is>
       </c>
     </row>
@@ -667,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13,28%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-7,68%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-4,46%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>-5,33%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -692,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -705,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 8,95</t>
+          <t>-15,69; 21,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,99; 15,43</t>
+          <t>-8,46; 41,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,65; 21,33</t>
+          <t>-22,05; 9,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 32,22</t>
+          <t>-24,5; 14,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,06; 9,19</t>
+          <t>-14,04; 9,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 17,26</t>
+          <t>-10,84; 19,32</t>
         </is>
       </c>
     </row>
@@ -747,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-12,54</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,41</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-18,54</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-6,03</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-12,54</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>-5,08</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -772,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,75</t>
+          <t>-2,22</t>
         </is>
       </c>
     </row>
@@ -785,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-26,4; -10,86</t>
+          <t>-19,14; -5,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 2,12</t>
+          <t>-8,63; 7,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,62; -6,18</t>
+          <t>-25,86; -11,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 7,56</t>
+          <t>-13,43; 2,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,23; -9,84</t>
+          <t>-20,46; -10,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 2,55</t>
+          <t>-7,93; 3,51</t>
         </is>
       </c>
     </row>
@@ -823,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-19,02%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-27,75%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-9,03%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-19,02%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>-7,6%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -848,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-4,15%</t>
+          <t>-3,34%</t>
         </is>
       </c>
     </row>
@@ -861,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,48; -17,08</t>
+          <t>-27,86; -8,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-21,08; 3,48</t>
+          <t>-12,09; 11,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,65; -9,96</t>
+          <t>-37,31; -18,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 12,11</t>
+          <t>-19,24; 4,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,59; -15,67</t>
+          <t>-29,94; -15,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 4,02</t>
+          <t>-11,57; 5,49</t>
         </is>
       </c>
     </row>
@@ -903,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-8,18</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-4,11</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-10,3</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2,92</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-8,18</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-6,12</t>
+          <t>2,59</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -928,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,26</t>
+          <t>-1,1</t>
         </is>
       </c>
     </row>
@@ -941,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,87; -0,85</t>
+          <t>-17,0; 0,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 11,84</t>
+          <t>-12,69; 5,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 0,24</t>
+          <t>-19,34; -1,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,03; 3,03</t>
+          <t>-6,4; 11,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,04; -2,57</t>
+          <t>-15,31; -2,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 4,22</t>
+          <t>-7,91; 5,09</t>
         </is>
       </c>
     </row>
@@ -979,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-13,92%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-7,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-16,22%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-13,92%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-10,41%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-3,69%</t>
+          <t>-1,81%</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-28,0; -1,44</t>
+          <t>-27,05; 1,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 20,73</t>
+          <t>-20,05; 9,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-26,65; 0,52</t>
+          <t>-28,84; -2,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 5,26</t>
+          <t>-9,42; 20,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-23,46; -4,6</t>
+          <t>-23,64; -3,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 7,14</t>
+          <t>-12,36; 8,84</t>
         </is>
       </c>
     </row>
@@ -1059,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-11,87</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-4,34</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-13,7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-2,36</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-11,87</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-6,49</t>
+          <t>-3,14</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1084,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,53</t>
+          <t>-3,78</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-22,49; -5,19</t>
+          <t>-20,27; -2,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 10,75</t>
+          <t>-13,44; 3,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,11; -3,06</t>
+          <t>-22,18; -4,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-17,49; 1,87</t>
+          <t>-11,83; 5,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-18,84; -6,58</t>
+          <t>-18,72; -6,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 3,6</t>
+          <t>-9,42; 2,94</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-18,41%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-6,73%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-21,33%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-3,68%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-18,41%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-10,06%</t>
+          <t>-4,9%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1160,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-7,04%</t>
+          <t>-5,87%</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,73; -8,52</t>
+          <t>-30,2; -4,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 18,17</t>
+          <t>-19,83; 5,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,94; -4,82</t>
+          <t>-33,69; -8,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,81; 3,37</t>
+          <t>-17,23; 9,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,49; -10,67</t>
+          <t>-28,24; -10,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-16,9; 5,78</t>
+          <t>-14,06; 4,82</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-9,09</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,77</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-12,62</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-1,85</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-9,09</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-3,24</t>
+          <t>-1,98</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1240,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,63</t>
+          <t>-1,9</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-16,94; -8,03</t>
+          <t>-13,06; -4,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 4,45</t>
+          <t>-6,6; 2,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,31; -5,0</t>
+          <t>-16,72; -7,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 1,5</t>
+          <t>-6,42; 2,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,77; -7,92</t>
+          <t>-13,92; -7,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 1,24</t>
+          <t>-5,06; 1,36</t>
         </is>
       </c>
     </row>
@@ -1291,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-14,69%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-2,87%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-19,61%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-2,87%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-14,69%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-5,24%</t>
+          <t>-3,07%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1316,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-4,18%</t>
+          <t>-3,01%</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-25,55; -12,95</t>
+          <t>-20,56; -8,01</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 6,93</t>
+          <t>-10,35; 4,63</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-20,81; -8,27</t>
+          <t>-25,27; -12,66</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 2,36</t>
+          <t>-9,59; 3,64</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-21,45; -12,79</t>
+          <t>-21,54; -12,49</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 1,99</t>
+          <t>-7,92; 2,21</t>
         </is>
       </c>
     </row>
